--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92565597787</v>
+        <v>46157.93089331215</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93089331215</v>
+        <v>46157.93167172303</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93167172303</v>
+        <v>46157.93397583146</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93397583146</v>
+        <v>46157.9371528979</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9371528979</v>
+        <v>46158.28213984113</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28213984113</v>
+        <v>46158.29675322781</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29675322781</v>
+        <v>46158.29811965532</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29811965532</v>
+        <v>46158.33384843736</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33384843736</v>
+        <v>46158.36854305492</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/32. Севэнко (тепловая энергия) Мира,59/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36854305492</v>
+        <v>46158.3728502328</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
